--- a/04_metadata_and_lineage/data-dictionary.xlsx
+++ b/04_metadata_and_lineage/data-dictionary.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\enterprise-data-governance-operating-system\04_metadata_and_lineage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74190F0E-1FC9-4592-BD8E-3F135F6E8298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7B11DF-53E1-4831-8E0F-CC723312499D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{82F7497E-E164-494A-BD9B-571A9BAB1192}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="1" xr2:uid="{82F7497E-E164-494A-BD9B-571A9BAB1192}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
     <sheet name="Dictionary" sheetId="2" r:id="rId2"/>
     <sheet name="Rules" sheetId="1" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Dictionary!$A$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Rules!$A$1:$E$6</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,11 +42,362 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="110">
+  <si>
+    <t>Data Dictionary Workbook</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Documents structural and business-facing metadata for datasets, tables, fields, and critical data elements.</t>
+  </si>
+  <si>
+    <t>How to use</t>
+  </si>
+  <si>
+    <t>Add one row per important field or governed attribute. Use this workbook to support reporting, quality controls, lineage, and onboarding.</t>
+  </si>
+  <si>
+    <t>Governance rule</t>
+  </si>
+  <si>
+    <t>Critical fields should identify source, definition, datatype, control relevance, and ownership context.</t>
+  </si>
+  <si>
+    <t>Asset ID</t>
+  </si>
+  <si>
+    <t>Asset Name</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Schema/Table</t>
+  </si>
+  <si>
+    <t>Field Name</t>
+  </si>
+  <si>
+    <t>Business Name</t>
+  </si>
+  <si>
+    <t>Business Definition</t>
+  </si>
+  <si>
+    <t>Datatype</t>
+  </si>
+  <si>
+    <t>Allowed Values / Rule</t>
+  </si>
+  <si>
+    <t>Nullable</t>
+  </si>
+  <si>
+    <t>Critical Data Element</t>
+  </si>
+  <si>
+    <t>Primary Key Flag</t>
+  </si>
+  <si>
+    <t>Classification</t>
+  </si>
+  <si>
+    <t>Source of Truth</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Steward</t>
+  </si>
+  <si>
+    <t>Refresh Frequency</t>
+  </si>
+  <si>
+    <t>Quality Rule Link</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>AST-001</t>
+  </si>
+  <si>
+    <t>Customer Master</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>dbo.customer_master</t>
+  </si>
+  <si>
+    <t>customer_id</t>
+  </si>
+  <si>
+    <t>Customer ID</t>
+  </si>
+  <si>
+    <t>Unique identifier for a customer record.</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Must be unique and non-null</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Internal</t>
+  </si>
+  <si>
+    <t>CRM Customer Master</t>
+  </si>
+  <si>
+    <t>Head of Customer Data</t>
+  </si>
+  <si>
+    <t>Customer Data Steward</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>DQ-002</t>
+  </si>
+  <si>
+    <t>Primary business identifier</t>
+  </si>
+  <si>
+    <t>customer_status</t>
+  </si>
+  <si>
+    <t>Customer Status</t>
+  </si>
+  <si>
+    <t>Current lifecycle status of the customer.</t>
+  </si>
+  <si>
+    <t>Must align to approved status code set</t>
+  </si>
+  <si>
+    <t>DQ-003</t>
+  </si>
+  <si>
+    <t>Reference-list controlled</t>
+  </si>
+  <si>
+    <t>AST-002</t>
+  </si>
+  <si>
+    <t>Service Request</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>ops.service_request</t>
+  </si>
+  <si>
+    <t>request_id</t>
+  </si>
+  <si>
+    <t>Service Request ID</t>
+  </si>
+  <si>
+    <t>Unique identifier for a service request.</t>
+  </si>
+  <si>
+    <t>Operations Intake System</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Operations Steward</t>
+  </si>
+  <si>
+    <t>Near real-time</t>
+  </si>
+  <si>
+    <t>Core operational key</t>
+  </si>
+  <si>
+    <t>request_date</t>
+  </si>
+  <si>
+    <t>Request Date</t>
+  </si>
+  <si>
+    <t>Date the service request was recorded.</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>Must fall within valid operational period</t>
+  </si>
+  <si>
+    <t>DQ-004</t>
+  </si>
+  <si>
+    <t>Supports timeliness reporting</t>
+  </si>
+  <si>
+    <t>AST-003</t>
+  </si>
+  <si>
+    <t>Executive Dashboard Mart</t>
+  </si>
+  <si>
+    <t>Reporting</t>
+  </si>
+  <si>
+    <t>rpt.executive_kpi_mart</t>
+  </si>
+  <si>
+    <t>active_customer_count</t>
+  </si>
+  <si>
+    <t>Active Customer Count</t>
+  </si>
+  <si>
+    <t>Certified KPI showing active customers in the approved reporting period.</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>Must align to approved KPI definition</t>
+  </si>
+  <si>
+    <t>Confidential</t>
+  </si>
+  <si>
+    <t>Certified Reporting Mart</t>
+  </si>
+  <si>
+    <t>Reporting Director</t>
+  </si>
+  <si>
+    <t>Reporting Steward</t>
+  </si>
+  <si>
+    <t>DQ-010</t>
+  </si>
+  <si>
+    <t>Business-rule sensitive</t>
+  </si>
+  <si>
+    <t>AST-004</t>
+  </si>
+  <si>
+    <t>Manual Adjustment Register</t>
+  </si>
+  <si>
+    <t>manual.adjustment_log</t>
+  </si>
+  <si>
+    <t>adjustment_reason</t>
+  </si>
+  <si>
+    <t>Adjustment Reason</t>
+  </si>
+  <si>
+    <t>Documented rationale for a manual adjustment.</t>
+  </si>
+  <si>
+    <t>Required when manual adjustment exists</t>
+  </si>
+  <si>
+    <t>Adjustment Register</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>DQ-012</t>
+  </si>
+  <si>
+    <t>Traceability control</t>
+  </si>
+  <si>
+    <t>Rule ID</t>
+  </si>
+  <si>
+    <t>Rule Name</t>
+  </si>
+  <si>
+    <t>Linked Fields / Assets</t>
+  </si>
+  <si>
+    <t>primary_key_uniqueness</t>
+  </si>
+  <si>
+    <t>customer_id; request_id</t>
+  </si>
+  <si>
+    <t>Ensures record-level uniqueness</t>
+  </si>
+  <si>
+    <t>Data Owner</t>
+  </si>
+  <si>
+    <t>valid_status_code</t>
+  </si>
+  <si>
+    <t>Ensures reference-list conformity</t>
+  </si>
+  <si>
+    <t>valid_date_range</t>
+  </si>
+  <si>
+    <t>Ensures valid date logic</t>
+  </si>
+  <si>
+    <t>approved_definition_alignment</t>
+  </si>
+  <si>
+    <t>Ensures KPI logic matches approved definition</t>
+  </si>
+  <si>
+    <t>manual_adjustment_traceability</t>
+  </si>
+  <si>
+    <t>Ensures manual changes are documented</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,8 +424,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -385,27 +742,609 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{806D537F-550E-40DE-9868-BFD96E897F0D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="28.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="110.73046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="135" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7BC42A-1CA7-463E-98C4-8985A7D83D27}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.46484375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="58.53125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.9296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.46484375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.53125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.06640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>41</v>
+      </c>
+      <c r="R3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O4" t="s">
+        <v>58</v>
+      </c>
+      <c r="P4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>60</v>
+      </c>
+      <c r="R4" t="s">
+        <v>42</v>
+      </c>
+      <c r="S4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" t="s">
+        <v>57</v>
+      </c>
+      <c r="O5" t="s">
+        <v>58</v>
+      </c>
+      <c r="P5" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>60</v>
+      </c>
+      <c r="R5" t="s">
+        <v>67</v>
+      </c>
+      <c r="S5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" t="s">
+        <v>78</v>
+      </c>
+      <c r="N6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O6" t="s">
+        <v>80</v>
+      </c>
+      <c r="P6" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>41</v>
+      </c>
+      <c r="R6" t="s">
+        <v>82</v>
+      </c>
+      <c r="S6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" t="s">
+        <v>90</v>
+      </c>
+      <c r="J7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" t="s">
+        <v>78</v>
+      </c>
+      <c r="N7" t="s">
+        <v>91</v>
+      </c>
+      <c r="O7" t="s">
+        <v>80</v>
+      </c>
+      <c r="P7" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>92</v>
+      </c>
+      <c r="R7" t="s">
+        <v>93</v>
+      </c>
+      <c r="S7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:S7" xr:uid="{CE7BC42A-1CA7-463E-98C4-8985A7D83D27}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4D1ACAE-130B-4783-94F1-62D33573FF96}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.53125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.53125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E6" xr:uid="{A4D1ACAE-130B-4783-94F1-62D33573FF96}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>